--- a/datos/centrales.xlsx
+++ b/datos/centrales.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,27 +430,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>central</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tecnologia</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>potencia_mw</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>anio_inicio</t>
         </is>
@@ -447,7 +459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Central Rio Manso Alto</t>
+          <t>Central Río Manso Alto</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,7 +469,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Biobio</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -470,7 +482,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Central Salto del Pehuen</t>
+          <t>Central Salto del Pehuén</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -480,7 +492,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Biobio</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -549,7 +561,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Biobio</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -677,7 +689,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Eolica Cerro Negro</t>
+          <t>Eólica Cerro Negro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,7 +712,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Eolica Punta Ventosa</t>
+          <t>Eólica Punta Ventosa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -723,7 +735,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Eolica Loma Larga</t>
+          <t>Eólica Loma Larga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -733,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Biobio</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -746,7 +758,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Eolica Vientos del Sur</t>
+          <t>Eólica Vientos del Sur</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -769,7 +781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Termoelectrica Bahia Norte</t>
+          <t>Termoeléctrica Bahía Norte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -792,7 +804,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Termoelectrica Valle Central</t>
+          <t>Termoeléctrica Valle Central</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -815,7 +827,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Termoelectrica Puerto Nuevo</t>
+          <t>Termoeléctrica Puerto Nuevo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -825,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -838,7 +850,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Termoelectrica Costa Brava</t>
+          <t>Termoeléctrica Costa Brava</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -848,7 +860,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Valparaiso</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -861,7 +873,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Termoelectrica Peninsula Gris</t>
+          <t>Termoeléctrica Península Gris</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -871,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Biobio</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -884,7 +896,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Diesel Respaldo Cordillera</t>
+          <t>Diésel Respaldo Cordillera</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,7 +931,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>nota</t>
         </is>

--- a/datos/centrales.xlsx
+++ b/datos/centrales.xlsx
@@ -476,13 +476,13 @@
         <v>420</v>
       </c>
       <c r="E2" t="n">
-        <v>1998</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Central Salto del Pehuén</t>
+          <t>Central Salto Verde</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -492,20 +492,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>310</v>
       </c>
       <c r="E3" t="n">
-        <v>2004</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Central Quebrada Azul</t>
+          <t>Central Aguas Claras</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -515,11 +515,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E4" t="n">
         <v>2011</v>
@@ -528,7 +528,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Central Lago Ventisquero</t>
+          <t>Central Vega Azul</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n">
         <v>2016</v>
@@ -551,7 +551,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Central Vega Escondida</t>
+          <t>Central Tres Saltos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E6" t="n">
         <v>1995</v>
@@ -591,13 +591,13 @@
         <v>230</v>
       </c>
       <c r="E7" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Parque Solar Llano Blanco</t>
+          <t>Parque Solar Llano Seco</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,20 +607,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="E8" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Parque Solar Salar Nuevo</t>
+          <t>Parque Solar Sol Naciente</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -630,20 +630,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>195</v>
+        <v>145</v>
       </c>
       <c r="E9" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Parque Solar Cerro Dorado</t>
+          <t>Parque Solar Quebrada Honda</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -657,16 +657,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="E10" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Parque Solar Media Luna</t>
+          <t>Parque Solar Altiplano</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -676,11 +676,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>310</v>
       </c>
       <c r="E11" t="n">
         <v>2023</v>
@@ -706,7 +706,7 @@
         <v>160</v>
       </c>
       <c r="E12" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="13">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E13" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Eólica Loma Larga</t>
+          <t>Eólica Loma Fría</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -745,20 +745,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E14" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Eólica Vientos del Sur</t>
+          <t>Eólica Campo Abierto</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -768,14 +768,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="E15" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="16">
@@ -791,20 +791,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>375</v>
       </c>
       <c r="E16" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Termoeléctrica Valle Central</t>
+          <t>Termoeléctrica Puerto Sur</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -814,20 +814,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>290</v>
       </c>
       <c r="E17" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Termoeléctrica Puerto Nuevo</t>
+          <t>Termoeléctrica Valle Central</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -837,20 +837,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>340</v>
+        <v>210</v>
       </c>
       <c r="E18" t="n">
-        <v>2003</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Termoeléctrica Costa Brava</t>
+          <t>Carboeléctrica Costa Brava</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -860,20 +860,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>480</v>
       </c>
       <c r="E19" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Termoeléctrica Península Gris</t>
+          <t>Carboeléctrica Roca Gris</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -883,14 +883,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E20" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="21">
@@ -913,7 +913,7 @@
         <v>45</v>
       </c>
       <c r="E21" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
     </row>
   </sheetData>
@@ -940,14 +940,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Datos sinteticos generados para el curso de Python de la Subsecretaria de Energia. Ninguna central corresponde a una instalacion real del Sistema Electrico Nacional.</t>
+          <t>Potencias declaradas al 31 de diciembre de 2024</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>La potencia esta expresada en MW y el anio de inicio corresponde a la entrada en operacion comercial simulada. Regenerar con scripts/generar_datos.py.</t>
+          <t>Las centrales de pasada se informan con su potencia máxima</t>
         </is>
       </c>
     </row>
